--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:57:18+00:00</t>
+    <t>2026-08-28T14:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-ops-strahlentherapie.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
